--- a/markdown_generator/portfolio.xlsx
+++ b/markdown_generator/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0934024A-0BF8-0145-9302-59999FB27CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B623FA-FFEE-6045-8B72-E6DD8F7E0EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>title</t>
   </si>
@@ -64,13 +64,29 @@
     <t>O2wCckGwbMs</t>
   </si>
   <si>
-    <t>Lei Wang (MSc student) and her AI co-presenter introduce our paper accepted by ICMI 2025.</t>
-  </si>
-  <si>
     <t>Talk</t>
   </si>
   <si>
-    <t>Lei Wang (MSc student) and her AI co-presenter introduce our paper accepted by ICMI 2025.
+    <t>b8Z3bn6-Dag</t>
+  </si>
+  <si>
+    <t>NeuroWise: A Multi-Agent LLM Glass-Box System for Practicing Double-Empathy Communication with Autistic Partners</t>
+  </si>
+  <si>
+    <t>Lei Wang (MSc student) and her AI co-presenter introduced our paper accepted by ICMI 2025.</t>
+  </si>
+  <si>
+    <t>Albert Tang (high school student) presented the demo of our paper accepted by CHI 2026.</t>
+  </si>
+  <si>
+    <t>Demo</t>
+  </si>
+  <si>
+    <t>Albert Tang (high school student) presented the demo of our paper accepted by CHI 2026.
+Interested in more details? Please see our paper at: https://dl.acm.org/doi/abs/10.1145/3772363.3798437</t>
+  </si>
+  <si>
+    <t>Lei Wang (MSc student) and her AI co-presenter introduced our paper accepted by ICMI 2025.
 Interested in more details? Please see our paper at: https://arxiv.org/pdf/2507.20300</t>
   </si>
 </sst>
@@ -457,15 +473,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="83" customWidth="1"/>
+    <col min="1" max="1" width="93.1640625" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="60" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="70" customWidth="1"/>
+    <col min="6" max="6" width="92.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -515,13 +531,31 @@
         <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>15</v>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/portfolio.xlsx
+++ b/markdown_generator/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B623FA-FFEE-6045-8B72-E6DD8F7E0EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B17B1B1-B8CB-7F46-892E-0493626534B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>title</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>NeuroWise: A Multi-Agent LLM Glass-Box System for Practicing Double-Empathy Communication with Autistic Partners</t>
-  </si>
-  <si>
-    <t>Lei Wang (MSc student) and her AI co-presenter introduced our paper accepted by ICMI 2025.</t>
   </si>
   <si>
     <t>Albert Tang (high school student) presented the demo of our paper accepted by CHI 2026.</t>
@@ -88,6 +85,22 @@
   <si>
     <t>Lei Wang (MSc student) and her AI co-presenter introduced our paper accepted by ICMI 2025.
 Interested in more details? Please see our paper at: https://arxiv.org/pdf/2507.20300</t>
+  </si>
+  <si>
+    <t>Trustworthy AI Psychotherapy: Multi-Agent LLM Workflow for Counseling and Explainable Mental Disorder Diagnosis</t>
+  </si>
+  <si>
+    <t>i6bKSkvH_OI</t>
+  </si>
+  <si>
+    <t>Lei Wang (master student) and her AI co-presenter introduced our paper accepted by ICMI 2025.</t>
+  </si>
+  <si>
+    <t>Mithat Can Ozgun (master student) presented the demo of our paper accepted by CIKM 2025.</t>
+  </si>
+  <si>
+    <t>Mithat Can Ozgun (master student) presented the demo of our paper accepted by CIKM 2025.
+Interested in more details? Please see our paper at: https://dl.acm.org/doi/abs/10.1145/3746252.3761164</t>
   </si>
 </sst>
 </file>
@@ -473,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="93.1640625" customWidth="1"/>
@@ -531,13 +544,13 @@
         <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -549,13 +562,31 @@
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>19</v>
+    </row>
+    <row r="5" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/portfolio.xlsx
+++ b/markdown_generator/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B17B1B1-B8CB-7F46-892E-0493626534B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7263EF5A-11C9-F144-B6EA-2713541586B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>title</t>
   </si>
@@ -101,6 +101,18 @@
   <si>
     <t>Mithat Can Ozgun (master student) presented the demo of our paper accepted by CIKM 2025.
 Interested in more details? Please see our paper at: https://dl.acm.org/doi/abs/10.1145/3746252.3761164</t>
+  </si>
+  <si>
+    <t>Immersive LEGO Co-Builder</t>
+  </si>
+  <si>
+    <t>KSMj4hYxoT4</t>
+  </si>
+  <si>
+    <t>Mikita Yurchyk (bachelor student) and his AI co-presenter introduced the demo of our Immersive LEGO Co-Builder.</t>
+  </si>
+  <si>
+    <t>Mikita Yurchyk (bachelor student) and his AI co-presenter introduced the demo of our Immersive LEGO Co-Builder, a mixed reality system that integrates Vision Language Models to deliver interactive, AI-assisted guidance for LEGO assembly.</t>
   </si>
 </sst>
 </file>
@@ -486,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="93.1640625" customWidth="1"/>
@@ -589,6 +601,24 @@
         <v>24</v>
       </c>
     </row>
+    <row r="6" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/markdown_generator/portfolio.xlsx
+++ b/markdown_generator/portfolio.xlsx
@@ -8,26 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7263EF5A-11C9-F144-B6EA-2713541586B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE771185-DCFB-CC48-B2F4-F32873DD9658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Portfolio!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>title</t>
   </si>
   <si>
+    <t>date</t>
+  </si>
+  <si>
     <t>image</t>
   </si>
   <si>
@@ -64,13 +67,20 @@
     <t>O2wCckGwbMs</t>
   </si>
   <si>
+    <t>Lei Wang (master student) and her AI co-presenter introduced our paper accepted by ICMI 2025.</t>
+  </si>
+  <si>
     <t>Talk</t>
   </si>
   <si>
+    <t>Lei Wang (MSc student) and her AI co-presenter introduced our paper accepted by ICMI 2025.
+Interested in more details? Please see our paper at: https://arxiv.org/pdf/2507.20300</t>
+  </si>
+  <si>
+    <t>NeuroWise: A Multi-Agent LLM Glass-Box System for Practicing Double-Empathy Communication with Autistic Partners</t>
+  </si>
+  <si>
     <t>b8Z3bn6-Dag</t>
-  </si>
-  <si>
-    <t>NeuroWise: A Multi-Agent LLM Glass-Box System for Practicing Double-Empathy Communication with Autistic Partners</t>
   </si>
   <si>
     <t>Albert Tang (high school student) presented the demo of our paper accepted by CHI 2026.</t>
@@ -83,17 +93,10 @@
 Interested in more details? Please see our paper at: https://dl.acm.org/doi/abs/10.1145/3772363.3798437</t>
   </si>
   <si>
-    <t>Lei Wang (MSc student) and her AI co-presenter introduced our paper accepted by ICMI 2025.
-Interested in more details? Please see our paper at: https://arxiv.org/pdf/2507.20300</t>
-  </si>
-  <si>
     <t>Trustworthy AI Psychotherapy: Multi-Agent LLM Workflow for Counseling and Explainable Mental Disorder Diagnosis</t>
   </si>
   <si>
     <t>i6bKSkvH_OI</t>
-  </si>
-  <si>
-    <t>Lei Wang (master student) and her AI co-presenter introduced our paper accepted by ICMI 2025.</t>
   </si>
   <si>
     <t>Mithat Can Ozgun (master student) presented the demo of our paper accepted by CIKM 2025.</t>
@@ -113,6 +116,21 @@
   </si>
   <si>
     <t>Mikita Yurchyk (bachelor student) and his AI co-presenter introduced the demo of our Immersive LEGO Co-Builder, a mixed reality system that integrates Vision Language Models to deliver interactive, AI-assisted guidance for LEGO assembly.</t>
+  </si>
+  <si>
+    <t>01/01/2025</t>
+  </si>
+  <si>
+    <t>01/07/2025</t>
+  </si>
+  <si>
+    <t>01/11/2025</t>
+  </si>
+  <si>
+    <t>21/02/2026</t>
+  </si>
+  <si>
+    <t>01/01/2026</t>
   </si>
 </sst>
 </file>
@@ -185,16 +203,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -498,18 +519,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="93.1640625" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="92.6640625" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="74.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -528,99 +550,117 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="B3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="59" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/markdown_generator/portfolio.xlsx
+++ b/markdown_generator/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE771185-DCFB-CC48-B2F4-F32873DD9658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8D77F1-9FE2-8C4B-97E9-7971D6BBF073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>title</t>
   </si>
@@ -131,6 +131,43 @@
   </si>
   <si>
     <t>01/01/2026</t>
+  </si>
+  <si>
+    <t>A Cooperative Memory Network for Personalized TDSs with Incomplete User Profiles</t>
+  </si>
+  <si>
+    <t>25/03/2021</t>
+  </si>
+  <si>
+    <t>VrjDw3LDSvU</t>
+  </si>
+  <si>
+    <t>Oral Talk</t>
+  </si>
+  <si>
+    <t>Jiahuan presented our paper accepted by The Web Conference 2021.</t>
+  </si>
+  <si>
+    <t>Jiahuan presented our paper accepted by The Web Conference 2021.
+Paper: https://arxiv.org/pdf/2102.08322.pdf
+Code: https://github.com/Jiahuan-Pei/CoMemNN</t>
+  </si>
+  <si>
+    <t>Retrospective and Prospective Mixture-of-Generators for Task-oriented Dialogue Response Generation</t>
+  </si>
+  <si>
+    <t>Eox36RKyaAQ</t>
+  </si>
+  <si>
+    <t>Jiahuan presented our paper accepted by ECAI 2020.</t>
+  </si>
+  <si>
+    <t>Jiahuan presented our paper accepted by ECAI 2020.
+Paper: https://arxiv.org/pdf/1911.08151.pdf
+Code: https://github.com/Jiahuan-Pei/multiwoz-mdrg</t>
+  </si>
+  <si>
+    <t>24/03/2021</t>
   </si>
 </sst>
 </file>
@@ -519,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -659,6 +696,48 @@
         <v>21</v>
       </c>
     </row>
+    <row r="7" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/markdown_generator/portfolio.xlsx
+++ b/markdown_generator/portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8D77F1-9FE2-8C4B-97E9-7971D6BBF073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F21D67-9F15-9640-9E96-F3811D239BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>title</t>
   </si>
@@ -73,10 +73,6 @@
     <t>Talk</t>
   </si>
   <si>
-    <t>Lei Wang (MSc student) and her AI co-presenter introduced our paper accepted by ICMI 2025.
-Interested in more details? Please see our paper at: https://arxiv.org/pdf/2507.20300</t>
-  </si>
-  <si>
     <t>NeuroWise: A Multi-Agent LLM Glass-Box System for Practicing Double-Empathy Communication with Autistic Partners</t>
   </si>
   <si>
@@ -89,10 +85,6 @@
     <t>Demo</t>
   </si>
   <si>
-    <t>Albert Tang (high school student) presented the demo of our paper accepted by CHI 2026.
-Interested in more details? Please see our paper at: https://dl.acm.org/doi/abs/10.1145/3772363.3798437</t>
-  </si>
-  <si>
     <t>Trustworthy AI Psychotherapy: Multi-Agent LLM Workflow for Counseling and Explainable Mental Disorder Diagnosis</t>
   </si>
   <si>
@@ -102,10 +94,6 @@
     <t>Mithat Can Ozgun (master student) presented the demo of our paper accepted by CIKM 2025.</t>
   </si>
   <si>
-    <t>Mithat Can Ozgun (master student) presented the demo of our paper accepted by CIKM 2025.
-Interested in more details? Please see our paper at: https://dl.acm.org/doi/abs/10.1145/3746252.3761164</t>
-  </si>
-  <si>
     <t>Immersive LEGO Co-Builder</t>
   </si>
   <si>
@@ -148,11 +136,6 @@
     <t>Jiahuan presented our paper accepted by The Web Conference 2021.</t>
   </si>
   <si>
-    <t>Jiahuan presented our paper accepted by The Web Conference 2021.
-Paper: https://arxiv.org/pdf/2102.08322.pdf
-Code: https://github.com/Jiahuan-Pei/CoMemNN</t>
-  </si>
-  <si>
     <t>Retrospective and Prospective Mixture-of-Generators for Task-oriented Dialogue Response Generation</t>
   </si>
   <si>
@@ -162,19 +145,344 @@
     <t>Jiahuan presented our paper accepted by ECAI 2020.</t>
   </si>
   <si>
-    <t>Jiahuan presented our paper accepted by ECAI 2020.
-Paper: https://arxiv.org/pdf/1911.08151.pdf
-Code: https://github.com/Jiahuan-Pei/multiwoz-mdrg</t>
-  </si>
-  <si>
     <t>24/03/2021</t>
+  </si>
+  <si>
+    <t>StoryMI: Steerable Multi-Agent Therapeutic Dialogue Generation</t>
+  </si>
+  <si>
+    <t>mcVM-8C8QQA</t>
+  </si>
+  <si>
+    <t>04/06/2026</t>
+  </si>
+  <si>
+    <t>Qingyu Meng (PhD student) presented our paper "StoryMI: Steerable Multi-Agent Therapeutic Dialogue Generation", accepted by ACL 2026.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lei Wang (MSc student) and her AI co-presenter introduced our paper accepted by ICMI 2025.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Interested in more details?  Please see our paper following resources.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Paper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: https://arxiv.org/pdf/2507.20300</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Albert Tang (high school student) presented the demo of our paper accepted by CHI 2026.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Interested in more details?  Please see our paper following resources. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Paper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: https://dl.acm.org/doi/abs/10.1145/3772363.3798437</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mithat Can Ozgun (master student) presented the demo of our paper accepted by CIKM 2025.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Interested in more details?  Please see our paper following resources.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Paper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: https://dl.acm.org/doi/abs/10.1145/3746252.3761164
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: https://github.com/mithatco/mental_health_multiagent</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jiahuan presented our paper accepted by The Web Conference 2021.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Interested in more details?  Please see our paper following resources.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Paper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: https://arxiv.org/pdf/2102.08322.pdf
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: https://github.com/Jiahuan-Pei/CoMemNN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jiahuan presented our paper accepted by ECAI 2020.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Interested in more details?  Please see our paper following resources.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Paper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: https://arxiv.org/pdf/1911.08151.pdf
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: https://github.com/Jiahuan-Pei/multiwoz-mdrg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Qingyu Meng (PhD student) presented our paper "StoryMI: Steerable Multi-Agent Therapeutic Dialogue Generation", accepted by ACL 2026.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Interested in more details?  Please see our paper following resources.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Paper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: https://arxiv.org/abs/2605.27393
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: https://github.com/Beren-sds/StoryMI</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,6 +498,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -240,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -253,6 +567,10 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -556,11 +874,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="2" max="2" width="14" style="5" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -572,7 +890,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -596,7 +914,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -617,7 +935,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
@@ -630,112 +948,133 @@
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="62" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/portfolio.xlsx
+++ b/markdown_generator/portfolio.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F21D67-9F15-9640-9E96-F3811D239BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF64FE19-4934-EB4E-965C-DCBF00D5BFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26240" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$9</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>title</t>
   </si>
@@ -43,12 +43,24 @@
     <t>tags</t>
   </si>
   <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
     <t>body</t>
   </si>
   <si>
     <t>Social AI Group Logo</t>
   </si>
   <si>
+    <t>01/01/2025</t>
+  </si>
+  <si>
     <t>/images/portfolio/Social AI@VU-logo.png</t>
   </si>
   <si>
@@ -64,6 +76,9 @@
     <t>Talking-to-Build: How LLM-Assisted Interface Shapes Player Performance and Experience in Minecraft</t>
   </si>
   <si>
+    <t>01/07/2025</t>
+  </si>
+  <si>
     <t>O2wCckGwbMs</t>
   </si>
   <si>
@@ -73,54 +88,48 @@
     <t>Talk</t>
   </si>
   <si>
+    <t>Trustworthy AI Psychotherapy: Multi-Agent LLM Workflow for Counseling and Explainable Mental Disorder Diagnosis</t>
+  </si>
+  <si>
+    <t>01/11/2025</t>
+  </si>
+  <si>
+    <t>i6bKSkvH_OI</t>
+  </si>
+  <si>
+    <t>Mithat Can Ozgun (master student) presented the demo of our paper accepted by CIKM 2025.</t>
+  </si>
+  <si>
+    <t>Demo</t>
+  </si>
+  <si>
+    <t>Immersive LEGO Co-Builder</t>
+  </si>
+  <si>
+    <t>01/01/2026</t>
+  </si>
+  <si>
+    <t>KSMj4hYxoT4</t>
+  </si>
+  <si>
+    <t>Mikita Yurchyk (bachelor student) and his AI co-presenter introduced the demo of our Immersive LEGO Co-Builder.</t>
+  </si>
+  <si>
+    <t>Mikita Yurchyk (bachelor student) and his AI co-presenter introduced the demo of our Immersive LEGO Co-Builder, a mixed reality system that integrates Vision Language Models to deliver interactive, AI-assisted guidance for LEGO assembly.</t>
+  </si>
+  <si>
     <t>NeuroWise: A Multi-Agent LLM Glass-Box System for Practicing Double-Empathy Communication with Autistic Partners</t>
   </si>
   <si>
+    <t>21/02/2026</t>
+  </si>
+  <si>
     <t>b8Z3bn6-Dag</t>
   </si>
   <si>
     <t>Albert Tang (high school student) presented the demo of our paper accepted by CHI 2026.</t>
   </si>
   <si>
-    <t>Demo</t>
-  </si>
-  <si>
-    <t>Trustworthy AI Psychotherapy: Multi-Agent LLM Workflow for Counseling and Explainable Mental Disorder Diagnosis</t>
-  </si>
-  <si>
-    <t>i6bKSkvH_OI</t>
-  </si>
-  <si>
-    <t>Mithat Can Ozgun (master student) presented the demo of our paper accepted by CIKM 2025.</t>
-  </si>
-  <si>
-    <t>Immersive LEGO Co-Builder</t>
-  </si>
-  <si>
-    <t>KSMj4hYxoT4</t>
-  </si>
-  <si>
-    <t>Mikita Yurchyk (bachelor student) and his AI co-presenter introduced the demo of our Immersive LEGO Co-Builder.</t>
-  </si>
-  <si>
-    <t>Mikita Yurchyk (bachelor student) and his AI co-presenter introduced the demo of our Immersive LEGO Co-Builder, a mixed reality system that integrates Vision Language Models to deliver interactive, AI-assisted guidance for LEGO assembly.</t>
-  </si>
-  <si>
-    <t>01/01/2025</t>
-  </si>
-  <si>
-    <t>01/07/2025</t>
-  </si>
-  <si>
-    <t>01/11/2025</t>
-  </si>
-  <si>
-    <t>21/02/2026</t>
-  </si>
-  <si>
-    <t>01/01/2026</t>
-  </si>
-  <si>
     <t>A Cooperative Memory Network for Personalized TDSs with Incomplete User Profiles</t>
   </si>
   <si>
@@ -133,349 +142,61 @@
     <t>Oral Talk</t>
   </si>
   <si>
-    <t>Jiahuan presented our paper accepted by The Web Conference 2021.</t>
-  </si>
-  <si>
     <t>Retrospective and Prospective Mixture-of-Generators for Task-oriented Dialogue Response Generation</t>
   </si>
   <si>
+    <t>24/03/2021</t>
+  </si>
+  <si>
     <t>Eox36RKyaAQ</t>
   </si>
   <si>
     <t>Jiahuan presented our paper accepted by ECAI 2020.</t>
   </si>
   <si>
-    <t>24/03/2021</t>
-  </si>
-  <si>
     <t>StoryMI: Steerable Multi-Agent Therapeutic Dialogue Generation</t>
   </si>
   <si>
+    <t>04/06/2026</t>
+  </si>
+  <si>
     <t>mcVM-8C8QQA</t>
   </si>
   <si>
-    <t>04/06/2026</t>
-  </si>
-  <si>
     <t>Qingyu Meng (PhD student) presented our paper "StoryMI: Steerable Multi-Agent Therapeutic Dialogue Generation", accepted by ACL 2026.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Lei Wang (MSc student) and her AI co-presenter introduced our paper accepted by ICMI 2025.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Interested in more details?  Please see our paper following resources.  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Paper</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: https://arxiv.org/pdf/2507.20300</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Albert Tang (high school student) presented the demo of our paper accepted by CHI 2026.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Interested in more details?  Please see our paper following resources. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Paper</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: https://dl.acm.org/doi/abs/10.1145/3772363.3798437</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mithat Can Ozgun (master student) presented the demo of our paper accepted by CIKM 2025.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Interested in more details?  Please see our paper following resources.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Paper</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: https://dl.acm.org/doi/abs/10.1145/3746252.3761164
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Code</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: https://github.com/mithatco/mental_health_multiagent</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Jiahuan presented our paper accepted by The Web Conference 2021.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Interested in more details?  Please see our paper following resources.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Paper</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: https://arxiv.org/pdf/2102.08322.pdf
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Code</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: https://github.com/Jiahuan-Pei/CoMemNN</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Jiahuan presented our paper accepted by ECAI 2020.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Interested in more details?  Please see our paper following resources.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Paper</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: https://arxiv.org/pdf/1911.08151.pdf
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Code</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: https://github.com/Jiahuan-Pei/multiwoz-mdrg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Qingyu Meng (PhD student) presented our paper "StoryMI: Steerable Multi-Agent Therapeutic Dialogue Generation", accepted by ACL 2026.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Interested in more details?  Please see our paper following resources.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Paper</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: https://arxiv.org/abs/2605.27393
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Code</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: https://github.com/Beren-sds/StoryMI</t>
-    </r>
+    <t>https://dl.acm.org/doi/abs/10.1145/3716553.3756015</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/abs/10.1145/3746252.3761164</t>
+  </si>
+  <si>
+    <t>https://github.com/mithatco/mental_health_multiagent</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/abs/10.1145/3772363.3798437</t>
+  </si>
+  <si>
+    <t>https://github.com/Jiahuan-Pei/CoMemNN</t>
+  </si>
+  <si>
+    <t>Jiahuan presented our paper accepted by TheWebConf 2021.</t>
+  </si>
+  <si>
+    <t>https://github.com/Jiahuan-Pei/multiwoz-mdrg</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/abs/10.1145/3442381.3449843C8</t>
+  </si>
+  <si>
+    <t>http://ecai2020.eu/papers/92_paper.pdf</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2605.27393</t>
+  </si>
+  <si>
+    <t>https://github.com/Beren-sds/StoryMI</t>
   </si>
 </sst>
 </file>
@@ -503,10 +224,12 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -551,29 +274,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -874,23 +595,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="14" style="5" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="74.33203125" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="9" width="35" customWidth="1"/>
+    <col min="10" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -908,177 +630,228 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>27</v>
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="59" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>26</v>
+      <c r="G5" s="4"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
+        <v>33</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="G8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="4" t="s">
         <v>43</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{5F5F0B8F-77AF-D245-B510-0F91F5277159}"/>
+    <hyperlink ref="G4" r:id="rId2" xr:uid="{49CCA4A7-8799-AD4C-815E-B8F9E68337D6}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{38125558-55D5-FA4B-A410-EE057C37FD52}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{E05D20E0-A0D9-EE4D-A693-20B21B708206}"/>
+    <hyperlink ref="G7" r:id="rId5" xr:uid="{602E3B9D-440A-C943-B74B-041D724E2A8E}"/>
+    <hyperlink ref="H7" r:id="rId6" xr:uid="{2CEF558F-65D9-CD4F-8273-F9878D1DFDD4}"/>
+    <hyperlink ref="H8" r:id="rId7" xr:uid="{58383DEF-1E85-304F-A44D-DD4C8F07D56A}"/>
+    <hyperlink ref="G8" r:id="rId8" xr:uid="{5D9868BD-6B2E-BE46-B324-DA23925E2515}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/markdown_generator/portfolio.xlsx
+++ b/markdown_generator/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF64FE19-4934-EB4E-965C-DCBF00D5BFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CF207C-6602-8D4C-89C0-85DB092B83F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="26240" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -187,9 +187,6 @@
     <t>https://github.com/Jiahuan-Pei/multiwoz-mdrg</t>
   </si>
   <si>
-    <t>https://dl.acm.org/doi/abs/10.1145/3442381.3449843C8</t>
-  </si>
-  <si>
     <t>http://ecai2020.eu/papers/92_paper.pdf</t>
   </si>
   <si>
@@ -197,6 +194,9 @@
   </si>
   <si>
     <t>https://github.com/Beren-sds/StoryMI</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/pdf/10.1145/3442381.3449843</t>
   </si>
 </sst>
 </file>
@@ -780,7 +780,7 @@
         <v>38</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>51</v>
@@ -806,7 +806,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>53</v>
@@ -832,10 +832,10 @@
         <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>

--- a/markdown_generator/portfolio.xlsx
+++ b/markdown_generator/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CF207C-6602-8D4C-89C0-85DB092B83F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A14A51A-3A3F-A34D-BD1A-BB97C578D9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="26240" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -163,9 +163,6 @@
     <t>mcVM-8C8QQA</t>
   </si>
   <si>
-    <t>Qingyu Meng (PhD student) presented our paper "StoryMI: Steerable Multi-Agent Therapeutic Dialogue Generation", accepted by ACL 2026.</t>
-  </si>
-  <si>
     <t>https://dl.acm.org/doi/abs/10.1145/3716553.3756015</t>
   </si>
   <si>
@@ -197,6 +194,9 @@
   </si>
   <si>
     <t>https://dl.acm.org/doi/pdf/10.1145/3442381.3449843</t>
+  </si>
+  <si>
+    <t>Qingyu Meng (PhD student) presented our paper accepted by ACL 2026.</t>
   </si>
 </sst>
 </file>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -675,14 +675,14 @@
       <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -699,17 +699,17 @@
       <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -725,7 +725,7 @@
       <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -749,14 +749,14 @@
       <c r="D6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -773,17 +773,17 @@
       <c r="D7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>52</v>
+      <c r="E7" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -799,17 +799,17 @@
       <c r="D8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -825,17 +825,17 @@
       <c r="D9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>46</v>
+      <c r="E9" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>

--- a/markdown_generator/portfolio.xlsx
+++ b/markdown_generator/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A14A51A-3A3F-A34D-BD1A-BB97C578D9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3562CB03-85A9-8240-86BC-A60348F19A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="26240" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t>title</t>
   </si>
@@ -197,6 +197,9 @@
   </si>
   <si>
     <t>Qingyu Meng (PhD student) presented our paper accepted by ACL 2026.</t>
+  </si>
+  <si>
+    <t>/images/portfolio/ecai2020.png</t>
   </si>
 </sst>
 </file>
@@ -795,7 +798,9 @@
       <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D8" s="3" t="s">
         <v>41</v>
       </c>
